--- a/Excel生成跳转返回超链接/datamapping.xlsx
+++ b/Excel生成跳转返回超链接/datamapping.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目录索引" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t01_acct_chnl_h_info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t01_agric_lead_corp_list" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t01_applr_contr_info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="目录索引" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="t01_acct_chnl_h_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="t01_agric_lead_corp_list" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="t01_applr_contr_info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="18.83203125" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -493,6 +493,10 @@
         </is>
       </c>
       <c r="F1" s="2">
+        <f>HYPERLINK("#目录索引!B1","返回")</f>
+        <v/>
+      </c>
+      <c r="G1" s="2">
         <f>HYPERLINK("#目录索引!B1","返回")</f>
         <v/>
       </c>
@@ -988,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="18.83203125" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -1006,6 +1010,10 @@
         </is>
       </c>
       <c r="F1" s="2">
+        <f>HYPERLINK("#目录索引!B2","返回")</f>
+        <v/>
+      </c>
+      <c r="G1" s="2">
         <f>HYPERLINK("#目录索引!B2","返回")</f>
         <v/>
       </c>
@@ -1533,7 +1541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="17.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1559,6 +1567,10 @@
         <f>HYPERLINK("#目录索引!B3","返回")</f>
         <v/>
       </c>
+      <c r="G1" s="2">
+        <f>HYPERLINK("#目录索引!B3","返回")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
